--- a/data/trans_camb/IP18E_R1-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP18E_R1-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>0.5125637803577998</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.325577551400693</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.265898735583738</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-11.66879564223766</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.8253748938833461</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.816007083876194</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-1.545401008724254</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.139292668842241</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.508183890106441</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-35.2693058104916</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.437986692173306</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-15.88415156773856</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>2.640987770538259</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.334436975750148</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.08442297601846277</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-1.413806286084719</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.6107637278390315</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.013056784190085</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.005247676592380508</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.02380948351780136</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.02299499215886616</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.1184182947291073</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.008413714449069975</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03889964933183479</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.01560664835861561</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.01152421450573307</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.04565818633513628</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.3600991670151729</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.02458753793223779</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1645079865256256</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.02733139770216325</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.04530817554079012</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-0.001056297398181831</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-0.01425110878126688</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.006256808395755755</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.01004626997962626</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.411290094417417</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.37565271780481</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.582193936575005</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6272495232819586</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.514369288855133</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.814173285753373</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-5.609907445472821</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.696642690132467</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.746636952799038</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-11.36710615015035</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-4.340633544713969</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.100153800883656</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.146464874740905</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.07418327120195</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.622268115355152</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.031567811774432</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.336018838925508</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>5.45660958221867</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.01485099611663564</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.02499897747894144</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.01684389932255023</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.00667764398285449</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.01602748786617142</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.01920049524150515</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.0583387724108017</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.09147197746638107</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.06028820859378897</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.1194216289690453</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04545680029713725</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.04371664870793336</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.02302771212568806</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.06500026075822476</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.0279646306391854</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.06532331694687449</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.01427240843288943</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.05802672926468282</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-0.5347343890031997</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2.892874458171313</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.840246112629818</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-8.915439986989171</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.216205021639327</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.006511412420997</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.451997778282887</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.497115230397278</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.469642395182895</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-22.75699270279129</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.4546624734472</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-9.376680794715931</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>4.642683778552346</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.738940060044521</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.709217037765222</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.644384321471974</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>4.678081275352683</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>3.61115096189343</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.005811249559021446</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.03143844077559757</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.03098601790783253</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.09726410041180049</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.01324194664011365</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.02184674177733945</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.06786771607370594</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.04619497755154407</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.01572327608845633</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.2443045095986939</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.02617226223240938</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.09990410490812417</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.05285602818185707</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.08552024673678743</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.08891417569391402</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.01804223125404208</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.05224871861402842</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.03977713584202801</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-2.664957014580338</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-9.928744597442785</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.915848707770118</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-13.15928453968473</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-2.36295462915862</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-11.43667753912095</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-10.19108409142253</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-27.84537644841631</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-10.33858956168477</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-30.77566699126499</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-7.952148642195847</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-23.44349864594322</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>5.985319711237969</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.955632875203491</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>6.090981272468475</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.1582884911959083</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.599515672793682</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-1.509988248446082</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.02983513515830624</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1111558030378423</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.0210453642824215</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1445531349685952</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.02623030224773096</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.1269544090517707</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.1106707297450875</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3193955491154399</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.1110929783654252</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.3318274978704686</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.08459973183016653</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.2540819874435821</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.06990305957091218</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.01933512611494242</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.07082516534895013</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.003013274264612929</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.04090376699997765</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.01719760892809642</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-0.4118037105548034</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-0.9644960849802708</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.6938285021266033</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-9.368364833401078</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.5491577905295086</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-4.56568688354081</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-2.277316908691427</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-5.426033570159317</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.834277536057547</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-16.26945235985336</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.093924612526342</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-8.377084647172895</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.501856272164319</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.444288167594362</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.491951847654533</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-3.809590922622933</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1.017559968944302</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-1.257521954250133</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.004359222186661887</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.0102098466449709</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.007329389244448659</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.09896450237708983</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.005807339231057959</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.04828210218040885</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.02390818704115982</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.05675605394076156</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.02970639964951294</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.1715726145550671</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.02199470472420683</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.08884665833151996</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.01607083402332911</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.02598159217028518</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.01599399958472819</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.04055331347072746</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.01081722216509653</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.01330376967355437</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
